--- a/Horarios 2025.xlsx
+++ b/Horarios 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\Estudios academicos\Sistemas-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Estudios\Sistemas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2998079-701A-4097-8D6A-DF2313E5CF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5814B8C3-A37F-41AF-A70E-D97C13016A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9F919EC-C4D0-4C2C-8C38-A5DEC8BFFCF3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A9F919EC-C4D0-4C2C-8C38-A5DEC8BFFCF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Horario</t>
   </si>
@@ -101,18 +90,12 @@
     <t>Investigación Operativa                                               Leale</t>
   </si>
   <si>
-    <t>Tecnologías para la Automatización                              Garnica</t>
-  </si>
-  <si>
     <t>Administración de Sist. de Información                                       Cucchiara</t>
   </si>
   <si>
     <t>07:15            a              08:45</t>
   </si>
   <si>
-    <t>11:20            a              12:50</t>
-  </si>
-  <si>
     <t>13:35            a              15:45</t>
   </si>
   <si>
@@ -123,6 +106,15 @@
   </si>
   <si>
     <t>21:05            a              22:35</t>
+  </si>
+  <si>
+    <t>Ingeniería y calidad de software</t>
+  </si>
+  <si>
+    <t>11:20            a              12:05</t>
+  </si>
+  <si>
+    <t>12:05            a              12:50</t>
   </si>
 </sst>
 </file>
@@ -425,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -439,6 +431,81 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -448,80 +515,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,9 +856,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7F7CD0-8BAC-4E7A-B7B8-B2F20D7D6EAD}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -881,511 +879,546 @@
       </c>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="31">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="31"/>
+    </row>
+    <row r="4" spans="1:7" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="27"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="28"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="31"/>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="31"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="28"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="31"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="31"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="28"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="31"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="31"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="31"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="28"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="31"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="27"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" spans="1:7" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="27"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="31"/>
+    </row>
+    <row r="20" spans="1:7" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="31"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="27"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="6">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="19"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="30">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="31"/>
+    </row>
+    <row r="25" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="27"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="31"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="31"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="31"/>
+    </row>
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="B29" s="13"/>
+      <c r="C29" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="31"/>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="27"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="31"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="27"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="31"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="28"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="32"/>
+    </row>
+    <row r="35" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="5">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="B35" s="13"/>
+      <c r="C35" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="30">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="27"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="31"/>
+    </row>
+    <row r="37" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="27"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="31"/>
+    </row>
+    <row r="38" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="27"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="31"/>
+    </row>
+    <row r="39" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="27"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="31"/>
+    </row>
+    <row r="40" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="28"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="31"/>
+    </row>
+    <row r="41" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="5">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="14" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="31"/>
+    </row>
+    <row r="42" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="31"/>
+    </row>
+    <row r="43" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="27"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="31"/>
+    </row>
+    <row r="44" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="27"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="31"/>
+    </row>
+    <row r="45" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="27"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="31"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="28"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="32"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C13"/>
+  <mergeCells count="66">
+    <mergeCell ref="G23:G34"/>
+    <mergeCell ref="G35:G46"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G2:G22"/>
+    <mergeCell ref="F11:F19"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="D23:D28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C35:C40"/>
     <mergeCell ref="E44:E46"/>
     <mergeCell ref="F44:F46"/>
     <mergeCell ref="B32:B34"/>
@@ -1402,49 +1435,16 @@
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="D35:D37"/>
     <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="C29:C34"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="D23:D28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C35:C40"/>
-    <mergeCell ref="C41:C46"/>
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="D2:D7"/>
     <mergeCell ref="D8:D16"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="G23:G34"/>
-    <mergeCell ref="G35:G46"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G2:G22"/>
-    <mergeCell ref="F14:F22"/>
+    <mergeCell ref="E8:E16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Horarios 2025.xlsx
+++ b/Horarios 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Estudios\Sistemas-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\Estudios_academicos\Sistemas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5814B8C3-A37F-41AF-A70E-D97C13016A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4BD2F6-A78D-4D61-B15A-EFD59F7CA721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A9F919EC-C4D0-4C2C-8C38-A5DEC8BFFCF3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9F919EC-C4D0-4C2C-8C38-A5DEC8BFFCF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Horario</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Legislación</t>
-  </si>
-  <si>
-    <t>Tecnologías para la Automatización    Bigatti</t>
   </si>
   <si>
     <t>08:45            a              09:30</t>
@@ -174,7 +171,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -413,11 +410,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -431,95 +454,107 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,9 +891,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7F7CD0-8BAC-4E7A-B7B8-B2F20D7D6EAD}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -879,531 +914,529 @@
       </c>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="36"/>
+      <c r="G2" s="34">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="34"/>
+    </row>
+    <row r="4" spans="1:7" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="34"/>
+    </row>
+    <row r="6" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="34"/>
+    </row>
+    <row r="7" spans="1:7" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="34"/>
+    </row>
+    <row r="8" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="34"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="34"/>
+    </row>
+    <row r="13" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="34"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="34"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="34"/>
+    </row>
+    <row r="16" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="34"/>
+    </row>
+    <row r="18" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="34"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="30"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="34"/>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="34"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="30"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="34"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="35"/>
+    </row>
+    <row r="23" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="31">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="31"/>
-    </row>
-    <row r="4" spans="1:7" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="31"/>
-    </row>
-    <row r="5" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="31"/>
-    </row>
-    <row r="7" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="28"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="31"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="31"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="31"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="28"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="31"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="31"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="31"/>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="31"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="31"/>
-    </row>
-    <row r="18" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="31"/>
-    </row>
-    <row r="19" spans="1:7" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="27"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="31"/>
-    </row>
-    <row r="20" spans="1:7" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="31"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="31"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="32"/>
-    </row>
-    <row r="23" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
+      <c r="E23" s="20"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="33">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="34"/>
+    </row>
+    <row r="25" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="30"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="34"/>
+    </row>
+    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="31"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="34"/>
+    </row>
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="23" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="30">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="31"/>
-    </row>
-    <row r="25" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="27"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="31"/>
-    </row>
-    <row r="26" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="31"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="31"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="28"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="31"/>
-    </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26" t="s">
+      <c r="D29" s="16"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="34"/>
+    </row>
+    <row r="30" spans="1:7" ht="7.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="34"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="30"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="34"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="30"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="34"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="30"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="34"/>
+    </row>
+    <row r="34" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="31"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="35"/>
+    </row>
+    <row r="35" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="22" t="s">
+      <c r="B35" s="15"/>
+      <c r="C35" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="31"/>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="31"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="27"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="27"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="31"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="31"/>
-    </row>
-    <row r="34" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="28"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="32"/>
-    </row>
-    <row r="35" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="26" t="s">
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="33">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="30"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="34"/>
+    </row>
+    <row r="37" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="30"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="34"/>
+    </row>
+    <row r="38" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="30"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="34"/>
+    </row>
+    <row r="39" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="30"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="34"/>
+    </row>
+    <row r="40" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="31"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="34"/>
+    </row>
+    <row r="41" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="22" t="s">
+      <c r="B41" s="15"/>
+      <c r="C41" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="30">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="31"/>
-    </row>
-    <row r="37" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="27"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="31"/>
-    </row>
-    <row r="38" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="31"/>
-    </row>
-    <row r="39" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="27"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="31"/>
-    </row>
-    <row r="40" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="28"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="31"/>
-    </row>
-    <row r="42" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="31"/>
-    </row>
-    <row r="43" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="27"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="31"/>
-    </row>
-    <row r="44" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="27"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="31"/>
-    </row>
-    <row r="45" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="31"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="28"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="32"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="34"/>
+    </row>
+    <row r="42" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="30"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="34"/>
+    </row>
+    <row r="43" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="30"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="34"/>
+    </row>
+    <row r="44" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="30"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="34"/>
+    </row>
+    <row r="45" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="30"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="34"/>
+    </row>
+    <row r="46" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="31"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="35"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="7:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
     <mergeCell ref="G23:G34"/>
     <mergeCell ref="G35:G46"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G2:G22"/>
     <mergeCell ref="F11:F19"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="F2:F7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="B11:B22"/>
-    <mergeCell ref="B2:B10"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C35:C40"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A40"/>
     <mergeCell ref="A41:A46"/>
     <mergeCell ref="A23:A28"/>
     <mergeCell ref="C41:C46"/>
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="C26:C28"/>
     <mergeCell ref="E26:E28"/>
     <mergeCell ref="F26:F28"/>
     <mergeCell ref="C29:C34"/>
@@ -1413,12 +1446,11 @@
     <mergeCell ref="F23:F25"/>
     <mergeCell ref="D23:D28"/>
     <mergeCell ref="B26:B28"/>
-    <mergeCell ref="F35:F37"/>
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="E29:E31"/>
     <mergeCell ref="F29:F31"/>
     <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C35:C40"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="E44:E46"/>
     <mergeCell ref="F44:F46"/>
     <mergeCell ref="B32:B34"/>
@@ -1445,6 +1477,7 @@
     <mergeCell ref="D2:D7"/>
     <mergeCell ref="D8:D16"/>
     <mergeCell ref="E8:E16"/>
+    <mergeCell ref="D17:D22"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
